--- a/jira_export_2026-07-07.xlsx
+++ b/jira_export_2026-07-07.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>144 h</t>
+          <t>161 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>80.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>254</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -1254,7 +1254,7 @@
         <v>1</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L7" s="12" t="inlineStr"/>
       <c r="M7" s="12" t="inlineStr"/>
@@ -1814,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L15" s="12" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>3207.7</v>
       </c>
       <c r="P15" s="13" t="n">
-        <v>2138.47</v>
+        <v>1603.85</v>
       </c>
     </row>
     <row r="16">
@@ -2606,7 +2606,7 @@
         <v>1</v>
       </c>
       <c r="K26" s="15" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="L26" s="15" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         <v>219.1</v>
       </c>
       <c r="P26" s="16" t="n">
-        <v>175.28</v>
+        <v>146.07</v>
       </c>
     </row>
     <row r="27">
@@ -2966,7 +2966,7 @@
         <v>1</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L31" s="12" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L35" s="12" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         <v>3</v>
       </c>
       <c r="K58" s="15" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="L58" s="15" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         <v>1375.2</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>392.91</v>
+        <v>305.6</v>
       </c>
     </row>
     <row r="59">
@@ -5550,7 +5550,7 @@
         <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L67" s="12" t="inlineStr">
         <is>
@@ -5569,7 +5569,7 @@
         <v>227.5</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>75.83</v>
+        <v>37.92</v>
       </c>
     </row>
     <row r="68">
@@ -7486,7 +7486,7 @@
         <v>6</v>
       </c>
       <c r="K94" s="15" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="L94" s="15" t="inlineStr">
         <is>
@@ -8414,7 +8414,7 @@
         <v>8</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="L107" s="12" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>19</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.12</v>
+        <v>0.62</v>
       </c>
       <c r="L132" s="15" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>19</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0.12</v>
+        <v>0.62</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>10055.38</v>
       </c>
       <c r="P146" s="19" t="n">
-        <v>108.44</v>
+        <v>96.47</v>
       </c>
     </row>
   </sheetData>
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>19.75</v>
@@ -11741,7 +11741,7 @@
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>69.5</v>
+        <v>74.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>15.75</v>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>15.3%</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11762,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>19.75</v>
+        <v>25.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>2.5</v>
@@ -11771,17 +11771,17 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>22.75</v>
+        <v>28.75</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.9%</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>28.25</v>
+        <v>32.5</v>
       </c>
     </row>
   </sheetData>
@@ -11878,10 +11878,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>402048</v>
+        <v>403098</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>204262</v>
+        <v>205312</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>197785</v>
@@ -11928,10 +11928,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>216129</v>
+        <v>217179</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>123477</v>
+        <v>124527</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>92652</v>
@@ -11957,14 +11957,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="31" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
     <col width="22" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="16" customWidth="1" min="8" max="8"/>
@@ -11981,7 +11981,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 4 commande(s)</t>
+          <t>Épics créées ce mois — 5 commande(s)</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
         </is>
       </c>
       <c r="I5" s="26" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="6">
@@ -12214,30 +12214,54 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="n"/>
-      <c r="C9" s="18" t="n"/>
-      <c r="D9" s="18" t="n"/>
-      <c r="E9" s="18" t="n"/>
-      <c r="F9" s="18" t="n"/>
-      <c r="G9" s="18" t="n"/>
-      <c r="H9" s="18" t="inlineStr">
-        <is>
-          <t>4 commande(s)</t>
-        </is>
-      </c>
-      <c r="I9" s="25" t="n">
-        <v>2285</v>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34499</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34495</t>
+        </is>
+      </c>
+      <c r="C9" s="15" t="inlineStr">
+        <is>
+          <t>07/07/2026</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CLICHY</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F9" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G9" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>00172678</t>
+        </is>
+      </c>
+      <c r="I9" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B10" s="18" t="n"/>
@@ -12248,17 +12272,17 @@
       <c r="G10" s="18" t="n"/>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t>0 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I10" s="25" t="n">
-        <v>0</v>
+        <v>3335</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B11" s="18" t="n"/>
@@ -12269,11 +12293,32 @@
       <c r="G11" s="18" t="n"/>
       <c r="H11" s="18" t="inlineStr">
         <is>
+          <t>1 commande(s)</t>
+        </is>
+      </c>
+      <c r="I11" s="25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
           <t>4 commande(s)</t>
         </is>
       </c>
-      <c r="I11" s="25" t="n">
-        <v>2285</v>
+      <c r="I12" s="25" t="n">
+        <v>3335</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-07.xlsx
+++ b/jira_export_2026-07-07.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>161 h</t>
+          <t>163 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>80.7%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -6910,7 +6910,7 @@
         <v>5</v>
       </c>
       <c r="K86" s="15" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
       <c r="L86" s="15" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>10055.38</v>
       </c>
       <c r="P146" s="19" t="n">
-        <v>96.47</v>
+        <v>96.01000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>54</v>
+        <v>54.5</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>19.75</v>
@@ -11741,7 +11741,7 @@
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>74.5</v>
+        <v>75</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>15.75</v>
@@ -11751,7 +11751,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>32.5</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-07.xlsx
+++ b/jira_export_2026-07-07.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>10,055 €</t>
+          <t>10,283 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2,192 €</t>
+          <t>2,419 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>163 h</t>
+          <t>175 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -942,7 +942,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P146"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -1598,7 +1598,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="L12" s="15" t="inlineStr">
         <is>
@@ -2894,7 +2894,7 @@
         <v>1</v>
       </c>
       <c r="K30" s="15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="L30" s="15" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>3</v>
       </c>
       <c r="K50" s="15" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="L50" s="15" t="inlineStr">
         <is>
@@ -5566,10 +5566,10 @@
         <v>1046.5</v>
       </c>
       <c r="O67" s="17" t="n">
-        <v>227.5</v>
+        <v>455</v>
       </c>
       <c r="P67" s="13" t="n">
-        <v>37.92</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="68">
@@ -8367,65 +8367,49 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-26782</t>
+          <t>PDMDEP-26831</t>
         </is>
       </c>
       <c r="B107" s="12" t="inlineStr">
         <is>
-          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
+          <t xml:space="preserve"> [CD74] - Maj Ref carto dans le cadre de la maintenance</t>
         </is>
       </c>
       <c r="C107" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D107" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+          <t>CD74</t>
         </is>
       </c>
       <c r="E107" s="12" t="inlineStr">
         <is>
-          <t>Déploiement LiEx</t>
-        </is>
-      </c>
-      <c r="F107" s="12" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
+          <t>MAJ carto</t>
+        </is>
+      </c>
+      <c r="F107" s="12" t="inlineStr"/>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H107" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Maintenance</t>
+        </is>
+      </c>
+      <c r="H107" s="12" t="inlineStr"/>
       <c r="I107" s="12" t="inlineStr">
         <is>
-          <t>03/11/2025</t>
+          <t>05/11/2025</t>
         </is>
       </c>
       <c r="J107" s="12" t="n">
         <v>8</v>
       </c>
       <c r="K107" s="12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L107" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-26783</t>
-        </is>
-      </c>
-      <c r="M107" s="12" t="inlineStr">
-        <is>
-          <t>00142659</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L107" s="12" t="inlineStr"/>
+      <c r="M107" s="12" t="inlineStr"/>
       <c r="N107" s="13" t="n">
         <v>0</v>
       </c>
@@ -8439,12 +8423,12 @@
     <row r="108">
       <c r="A108" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24866</t>
+          <t>PDMDEP-26813</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
+          <t>[VILLEJUIF] - Litteralis Modèle facture + param Civil Net</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
@@ -8454,7 +8438,7 @@
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E108" s="15" t="n">
@@ -8472,34 +8456,34 @@
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>16/10/2025</t>
+          <t>04/11/2025</t>
         </is>
       </c>
       <c r="J108" s="15" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K108" s="15" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27017</t>
+          <t>PDMDEP-26814</t>
         </is>
       </c>
       <c r="M108" s="15" t="inlineStr">
         <is>
-          <t>00141205</t>
+          <t>00142941</t>
         </is>
       </c>
       <c r="N108" s="16" t="n">
-        <v>1212</v>
-      </c>
-      <c r="O108" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P108" s="16" t="n">
@@ -8509,26 +8493,28 @@
     <row r="109">
       <c r="A109" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24765</t>
+          <t>PDMDEP-26782</t>
         </is>
       </c>
       <c r="B109" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
+          <t>[FONTENAY SOUS BOIS] - LITTERALIS</t>
         </is>
       </c>
       <c r="C109" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v/>
+          <t>COMMUNE DE FONTENAY SOUS BOIS</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement LiEx</t>
+        </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
         <is>
@@ -8542,28 +8528,28 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I109" s="12" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>03/11/2025</t>
         </is>
       </c>
       <c r="J109" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K109" s="12" t="n">
-        <v>0.5</v>
+        <v>3.5</v>
       </c>
       <c r="L109" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28062</t>
+          <t>PDMDEP-26783</t>
         </is>
       </c>
       <c r="M109" s="12" t="inlineStr">
         <is>
-          <t>500768</t>
+          <t>00142659</t>
         </is>
       </c>
       <c r="N109" s="13" t="n">
@@ -8579,22 +8565,22 @@
     <row r="110">
       <c r="A110" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24426</t>
+          <t>PDMDEP-24866</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
         <is>
-          <t>[DRANCY] - Migration STD vers Exp</t>
+          <t>[MAUGES SUR LOIRE] - LITTERALIS</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE DRANCY</t>
+          <t>COMMUNE NOUVELLE DE MAUGES SUR LOIRE</t>
         </is>
       </c>
       <c r="E110" s="15" t="n">
@@ -8612,34 +8598,34 @@
       </c>
       <c r="H110" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
         <is>
-          <t>30/09/2025</t>
+          <t>16/10/2025</t>
         </is>
       </c>
       <c r="J110" s="15" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K110" s="15" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27028</t>
+          <t>PDMDEP-27017</t>
         </is>
       </c>
       <c r="M110" s="15" t="inlineStr">
         <is>
-          <t>500950</t>
+          <t>00141205</t>
         </is>
       </c>
       <c r="N110" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O110" s="16" t="n">
+        <v>1212</v>
+      </c>
+      <c r="O110" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P110" s="16" t="n">
@@ -8649,22 +8635,22 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24765</t>
         </is>
       </c>
       <c r="B111" s="12" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[COLOMBES] -  Litteralis - Interface Pastell</t>
         </is>
       </c>
       <c r="C111" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="E111" s="12" t="n">
@@ -8682,28 +8668,28 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I111" s="12" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="J111" s="12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K111" s="12" t="n">
-        <v>1.38</v>
+        <v>0.5</v>
       </c>
       <c r="L111" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27996</t>
+          <t>PDMDEP-28062</t>
         </is>
       </c>
       <c r="M111" s="12" t="inlineStr">
         <is>
-          <t>501219</t>
+          <t>500768</t>
         </is>
       </c>
       <c r="N111" s="13" t="n">
@@ -8719,12 +8705,12 @@
     <row r="112">
       <c r="A112" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24426</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>[DRANCY] - Migration STD vers Exp</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -8734,7 +8720,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
+          <t>VILLE DE DRANCY</t>
         </is>
       </c>
       <c r="E112" s="15" t="n">
@@ -8752,28 +8738,28 @@
       </c>
       <c r="H112" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>30/09/2025</t>
         </is>
       </c>
       <c r="J112" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K112" s="15" t="n">
-        <v>1.38</v>
+        <v>0.25</v>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27028</t>
         </is>
       </c>
       <c r="M112" s="15" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>500950</t>
         </is>
       </c>
       <c r="N112" s="16" t="n">
@@ -8789,22 +8775,22 @@
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B113" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C113" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D113" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E113" s="12" t="n">
@@ -8827,29 +8813,29 @@
       </c>
       <c r="I113" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J113" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K113" s="12" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="L113" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M113" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N113" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P113" s="13" t="n">
@@ -8859,22 +8845,22 @@
     <row r="114">
       <c r="A114" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C114" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E114" s="15" t="n">
@@ -8882,7 +8868,7 @@
       </c>
       <c r="F114" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G114" s="15" t="inlineStr">
@@ -8892,34 +8878,34 @@
       </c>
       <c r="H114" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J114" s="15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K114" s="15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M114" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N114" s="16" t="n">
-        <v>964.1</v>
-      </c>
-      <c r="O114" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O114" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P114" s="16" t="n">
@@ -8929,22 +8915,22 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B115" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C115" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E115" s="12" t="n">
@@ -8952,7 +8938,7 @@
       </c>
       <c r="F115" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -8962,35 +8948,35 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I115" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J115" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K115" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M115" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N115" s="13" t="n">
-        <v>140.4</v>
+        <v>2323</v>
       </c>
       <c r="O115" s="17" t="n">
-        <v>70.2</v>
+        <v>0</v>
       </c>
       <c r="P115" s="13" t="n">
         <v>0</v>
@@ -8999,17 +8985,17 @@
     <row r="116">
       <c r="A116" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C116" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
@@ -9022,7 +9008,7 @@
       </c>
       <c r="F116" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G116" s="15" t="inlineStr">
@@ -9037,29 +9023,29 @@
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J116" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K116" s="15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L116" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M116" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N116" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O116" s="16" t="n">
+        <v>964.1</v>
+      </c>
+      <c r="O116" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P116" s="16" t="n">
@@ -9069,22 +9055,22 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B117" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C117" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E117" s="12" t="n">
@@ -9092,7 +9078,7 @@
       </c>
       <c r="F117" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G117" s="12" t="inlineStr">
@@ -9102,35 +9088,35 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I117" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J117" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K117" s="12" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L117" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M117" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N117" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" s="13" t="n">
-        <v>0</v>
+        <v>140.4</v>
+      </c>
+      <c r="O117" s="17" t="n">
+        <v>70.2</v>
       </c>
       <c r="P117" s="13" t="n">
         <v>0</v>
@@ -9139,22 +9125,22 @@
     <row r="118">
       <c r="A118" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C118" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E118" s="15" t="n">
@@ -9172,28 +9158,28 @@
       </c>
       <c r="H118" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J118" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K118" s="15" t="n">
-        <v>0.12</v>
+        <v>2</v>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M118" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N118" s="16" t="n">
@@ -9224,7 +9210,7 @@
       </c>
       <c r="D119" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E119" s="12" t="n">
@@ -9258,12 +9244,12 @@
       </c>
       <c r="L119" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M119" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N119" s="13" t="n">
@@ -9328,12 +9314,12 @@
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M120" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N120" s="16" t="n">
@@ -9349,12 +9335,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B121" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C121" s="12" t="inlineStr">
@@ -9364,7 +9350,7 @@
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E121" s="12" t="n">
@@ -9382,28 +9368,28 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I121" s="12" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J121" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K121" s="12" t="n">
-        <v>0.5</v>
+        <v>0.12</v>
       </c>
       <c r="L121" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M121" s="12" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N121" s="13" t="n">
@@ -9419,22 +9405,22 @@
     <row r="122">
       <c r="A122" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C122" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E122" s="15" t="n">
@@ -9442,7 +9428,7 @@
       </c>
       <c r="F122" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G122" s="15" t="inlineStr">
@@ -9452,34 +9438,34 @@
       </c>
       <c r="H122" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J122" s="15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K122" s="15" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M122" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N122" s="16" t="n">
-        <v>482.72</v>
-      </c>
-      <c r="O122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O122" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P122" s="16" t="n">
@@ -9489,22 +9475,22 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B123" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C123" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E123" s="12" t="n">
@@ -9522,28 +9508,28 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I123" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J123" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="K123" s="12" t="n">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="L123" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M123" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N123" s="13" t="n">
@@ -9559,22 +9545,22 @@
     <row r="124">
       <c r="A124" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
         </is>
       </c>
       <c r="C124" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E124" s="15" t="n">
@@ -9582,7 +9568,7 @@
       </c>
       <c r="F124" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G124" s="15" t="inlineStr">
@@ -9597,27 +9583,27 @@
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J124" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K124" s="15" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M124" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N124" s="16" t="n">
-        <v>250</v>
+        <v>482.72</v>
       </c>
       <c r="O124" s="17" t="n">
         <v>0</v>
@@ -9629,12 +9615,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B125" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C125" s="12" t="inlineStr">
@@ -9644,7 +9630,7 @@
       </c>
       <c r="D125" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E125" s="12" t="n">
@@ -9662,34 +9648,34 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I125" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J125" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K125" s="12" t="n">
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="L125" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M125" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N125" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O125" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P125" s="13" t="n">
@@ -9699,12 +9685,12 @@
     <row r="126">
       <c r="A126" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B126" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C126" s="15" t="inlineStr">
@@ -9714,7 +9700,7 @@
       </c>
       <c r="D126" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E126" s="15" t="n">
@@ -9730,24 +9716,36 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H126" s="15" t="inlineStr"/>
+      <c r="H126" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I126" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J126" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L126" s="15" t="inlineStr"/>
-      <c r="M126" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L126" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28035</t>
+        </is>
+      </c>
+      <c r="M126" s="15" t="inlineStr">
+        <is>
+          <t>468660</t>
+        </is>
+      </c>
       <c r="N126" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O126" s="16" t="n">
+        <v>250</v>
+      </c>
+      <c r="O126" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P126" s="16" t="n">
@@ -9757,12 +9755,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B127" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C127" s="12" t="inlineStr">
@@ -9772,7 +9770,7 @@
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E127" s="12" t="n">
@@ -9795,29 +9793,29 @@
       </c>
       <c r="I127" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J127" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K127" s="12" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="L127" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M127" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N127" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O127" s="13" t="n">
+        <v>230</v>
+      </c>
+      <c r="O127" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P127" s="13" t="n">
@@ -9827,22 +9825,22 @@
     <row r="128">
       <c r="A128" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B128" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C128" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D128" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E128" s="15" t="n">
@@ -9858,32 +9856,20 @@
           <t>Projet</t>
         </is>
       </c>
-      <c r="H128" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H128" s="15" t="inlineStr"/>
       <c r="I128" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J128" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K128" s="15" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="L128" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27377</t>
-        </is>
-      </c>
-      <c r="M128" s="15" t="inlineStr">
-        <is>
-          <t>478048</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L128" s="15" t="inlineStr"/>
+      <c r="M128" s="15" t="inlineStr"/>
       <c r="N128" s="16" t="n">
         <v>0</v>
       </c>
@@ -9897,12 +9883,12 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B129" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C129" s="12" t="inlineStr">
@@ -9912,7 +9898,7 @@
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E129" s="12" t="n">
@@ -9930,28 +9916,28 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I129" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J129" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K129" s="12" t="n">
         <v>0.25</v>
       </c>
       <c r="L129" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M129" s="12" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N129" s="13" t="n">
@@ -9967,12 +9953,12 @@
     <row r="130">
       <c r="A130" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B130" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C130" s="15" t="inlineStr">
@@ -9982,7 +9968,7 @@
       </c>
       <c r="D130" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E130" s="15" t="n">
@@ -9995,7 +9981,7 @@
       </c>
       <c r="G130" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H130" s="15" t="inlineStr">
@@ -10005,17 +9991,25 @@
       </c>
       <c r="I130" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J130" s="15" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K130" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L130" s="15" t="inlineStr"/>
-      <c r="M130" s="15" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="L130" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27377</t>
+        </is>
+      </c>
+      <c r="M130" s="15" t="inlineStr">
+        <is>
+          <t>478048</t>
+        </is>
+      </c>
       <c r="N130" s="16" t="n">
         <v>0</v>
       </c>
@@ -10029,22 +10023,22 @@
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B131" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C131" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D131" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>COMMUNE D'ARCUEIL</t>
         </is>
       </c>
       <c r="E131" s="12" t="n">
@@ -10052,7 +10046,7 @@
       </c>
       <c r="F131" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -10062,34 +10056,34 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I131" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J131" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K131" s="12" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="L131" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28019</t>
+          <t>PDMDEP-27535</t>
         </is>
       </c>
       <c r="M131" s="12" t="inlineStr">
         <is>
-          <t>455151</t>
+          <t>465345</t>
         </is>
       </c>
       <c r="N131" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P131" s="13" t="n">
@@ -10099,12 +10093,12 @@
     <row r="132">
       <c r="A132" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B132" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C132" s="15" t="inlineStr">
@@ -10114,7 +10108,7 @@
       </c>
       <c r="D132" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E132" s="15" t="n">
@@ -10127,35 +10121,27 @@
       </c>
       <c r="G132" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H132" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I132" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J132" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K132" s="15" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="L132" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34362</t>
-        </is>
-      </c>
-      <c r="M132" s="15" t="inlineStr">
-        <is>
-          <t>458057</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L132" s="15" t="inlineStr"/>
+      <c r="M132" s="15" t="inlineStr"/>
       <c r="N132" s="16" t="n">
         <v>0</v>
       </c>
@@ -10169,22 +10155,22 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B133" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C133" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D133" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E133" s="12" t="n">
@@ -10192,7 +10178,7 @@
       </c>
       <c r="F133" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -10202,34 +10188,34 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I133" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J133" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K133" s="12" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L133" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M133" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N133" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O133" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O133" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P133" s="13" t="n">
@@ -10239,22 +10225,22 @@
     <row r="134">
       <c r="A134" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B134" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C134" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D134" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E134" s="15" t="n">
@@ -10262,32 +10248,40 @@
       </c>
       <c r="F134" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G134" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H134" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I134" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J134" s="15" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K134" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L134" s="15" t="inlineStr"/>
-      <c r="M134" s="15" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L134" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34362</t>
+        </is>
+      </c>
+      <c r="M134" s="15" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N134" s="16" t="n">
         <v>0</v>
       </c>
@@ -10301,22 +10295,22 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B135" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C135" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D135" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E135" s="12" t="n">
@@ -10329,7 +10323,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H135" s="12" t="inlineStr">
@@ -10339,17 +10333,25 @@
       </c>
       <c r="I135" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J135" s="12" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="K135" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L135" s="12" t="inlineStr"/>
-      <c r="M135" s="12" t="inlineStr"/>
+        <v>0.62</v>
+      </c>
+      <c r="L135" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28020</t>
+        </is>
+      </c>
+      <c r="M135" s="12" t="inlineStr">
+        <is>
+          <t>458057</t>
+        </is>
+      </c>
       <c r="N135" s="13" t="n">
         <v>0</v>
       </c>
@@ -10363,22 +10365,22 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E136" s="15" t="n">
@@ -10386,7 +10388,7 @@
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G136" s="15" t="inlineStr">
@@ -10396,19 +10398,19 @@
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="L136" s="15" t="inlineStr"/>
       <c r="M136" s="15" t="inlineStr"/>
@@ -10425,22 +10427,22 @@
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B137" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C137" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D137" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E137" s="12" t="n">
@@ -10463,14 +10465,14 @@
       </c>
       <c r="I137" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J137" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="K137" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L137" s="12" t="inlineStr"/>
       <c r="M137" s="12" t="inlineStr"/>
@@ -10487,22 +10489,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10520,19 +10522,19 @@
       </c>
       <c r="H138" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>6.75</v>
+        <v>1.25</v>
       </c>
       <c r="L138" s="15" t="inlineStr"/>
       <c r="M138" s="15" t="inlineStr"/>
@@ -10549,12 +10551,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
@@ -10564,7 +10566,7 @@
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10577,7 +10579,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H139" s="12" t="inlineStr">
@@ -10587,25 +10589,17 @@
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L139" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M139" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L139" s="12" t="inlineStr"/>
+      <c r="M139" s="12" t="inlineStr"/>
       <c r="N139" s="13" t="n">
         <v>0</v>
       </c>
@@ -10619,12 +10613,12 @@
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
@@ -10634,7 +10628,7 @@
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10657,14 +10651,14 @@
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0.5</v>
+        <v>6.75</v>
       </c>
       <c r="L140" s="15" t="inlineStr"/>
       <c r="M140" s="15" t="inlineStr"/>
@@ -10681,12 +10675,12 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -10696,13 +10690,11 @@
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E141" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>FOUGERES</t>
+        </is>
+      </c>
+      <c r="E141" s="12" t="n">
+        <v/>
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
@@ -10711,27 +10703,35 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L141" s="12" t="inlineStr"/>
-      <c r="M141" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L141" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
@@ -10745,28 +10745,26 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
-        </is>
-      </c>
-      <c r="E142" s="15" t="inlineStr">
-        <is>
-          <t>Modélisation spécifique</t>
-        </is>
+          <t>LE MANS METROPOLE</t>
+        </is>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v/>
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
@@ -10780,19 +10778,19 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L142" s="15" t="inlineStr"/>
       <c r="M142" s="15" t="inlineStr"/>
@@ -10809,23 +10807,27 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C143" s="12" t="inlineStr"/>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E143" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
@@ -10845,14 +10847,14 @@
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="L143" s="12" t="inlineStr"/>
       <c r="M143" s="12" t="inlineStr"/>
@@ -10869,21 +10871,29 @@
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="C144" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C144" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
-        </is>
-      </c>
-      <c r="E144" s="15" t="inlineStr"/>
+          <t>CD14</t>
+        </is>
+      </c>
+      <c r="E144" s="15" t="inlineStr">
+        <is>
+          <t>Modélisation spécifique</t>
+        </is>
+      </c>
       <c r="F144" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -10891,35 +10901,31 @@
       </c>
       <c r="G144" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H144" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H144" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L144" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-33362</t>
-        </is>
-      </c>
-      <c r="M144" s="15" t="inlineStr">
-        <is>
-          <t>00167140</t>
-        </is>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="L144" s="15" t="inlineStr"/>
+      <c r="M144" s="15" t="inlineStr"/>
       <c r="N144" s="16" t="n">
-        <v>510.6</v>
-      </c>
-      <c r="O144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O144" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P144" s="16" t="n">
@@ -10929,89 +10935,209 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t>PSC-1228</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B145" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MERLEVENEZ</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr"/>
       <c r="D145" s="12" t="inlineStr">
         <is>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E145" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
+      <c r="F145" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G145" s="12" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H145" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="I145" s="12" t="inlineStr">
+        <is>
+          <t>03/09/2023</t>
+        </is>
+      </c>
+      <c r="J145" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K145" s="12" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="L145" s="12" t="inlineStr"/>
+      <c r="M145" s="12" t="inlineStr"/>
+      <c r="N145" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O145" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="14" t="inlineStr">
+        <is>
+          <t>PSC-1270</t>
+        </is>
+      </c>
+      <c r="B146" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="C146" s="15" t="inlineStr"/>
+      <c r="D146" s="15" t="inlineStr">
+        <is>
+          <t>COMMUNE DE CASTELNAUDARY</t>
+        </is>
+      </c>
+      <c r="E146" s="15" t="inlineStr"/>
+      <c r="F146" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G146" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="inlineStr"/>
+      <c r="I146" s="15" t="inlineStr">
+        <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="J146" s="15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K146" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L146" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33362</t>
+        </is>
+      </c>
+      <c r="M146" s="15" t="inlineStr">
+        <is>
+          <t>00167140</t>
+        </is>
+      </c>
+      <c r="N146" s="16" t="n">
+        <v>510.6</v>
+      </c>
+      <c r="O146" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="inlineStr">
+        <is>
+          <t>PSC-1228</t>
+        </is>
+      </c>
+      <c r="B147" s="12" t="inlineStr">
+        <is>
           <t>MAIRIE DE MERLEVENEZ</t>
         </is>
       </c>
-      <c r="E145" s="12" t="inlineStr"/>
-      <c r="F145" s="12" t="inlineStr">
+      <c r="C147" s="12" t="inlineStr"/>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>MAIRIE DE MERLEVENEZ</t>
+        </is>
+      </c>
+      <c r="E147" s="12" t="inlineStr"/>
+      <c r="F147" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="G145" s="12" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H145" s="12" t="inlineStr"/>
-      <c r="I145" s="12" t="inlineStr">
+      <c r="G147" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H147" s="12" t="inlineStr"/>
+      <c r="I147" s="12" t="inlineStr">
         <is>
           <t>09/04/2026</t>
         </is>
       </c>
-      <c r="J145" s="12" t="n">
+      <c r="J147" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K145" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L145" s="12" t="inlineStr">
+      <c r="K147" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L147" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-32829</t>
         </is>
       </c>
-      <c r="M145" s="12" t="inlineStr">
+      <c r="M147" s="12" t="inlineStr">
         <is>
           <t>00163534</t>
         </is>
       </c>
-      <c r="N145" s="13" t="n">
+      <c r="N147" s="13" t="n">
         <v>50</v>
       </c>
-      <c r="O145" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P145" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="18" t="inlineStr">
+      <c r="O147" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B146" s="18" t="inlineStr"/>
-      <c r="C146" s="18" t="inlineStr"/>
-      <c r="D146" s="18" t="inlineStr"/>
-      <c r="E146" s="18" t="inlineStr"/>
-      <c r="F146" s="18" t="inlineStr"/>
-      <c r="G146" s="18" t="inlineStr"/>
-      <c r="H146" s="18" t="inlineStr"/>
-      <c r="I146" s="18" t="inlineStr"/>
-      <c r="J146" s="18" t="inlineStr"/>
-      <c r="K146" s="18" t="inlineStr"/>
-      <c r="L146" s="18" t="inlineStr"/>
-      <c r="M146" s="18" t="inlineStr"/>
-      <c r="N146" s="19" t="n">
+      <c r="B148" s="18" t="inlineStr"/>
+      <c r="C148" s="18" t="inlineStr"/>
+      <c r="D148" s="18" t="inlineStr"/>
+      <c r="E148" s="18" t="inlineStr"/>
+      <c r="F148" s="18" t="inlineStr"/>
+      <c r="G148" s="18" t="inlineStr"/>
+      <c r="H148" s="18" t="inlineStr"/>
+      <c r="I148" s="18" t="inlineStr"/>
+      <c r="J148" s="18" t="inlineStr"/>
+      <c r="K148" s="18" t="inlineStr"/>
+      <c r="L148" s="18" t="inlineStr"/>
+      <c r="M148" s="18" t="inlineStr"/>
+      <c r="N148" s="19" t="n">
         <v>68470.25999999999</v>
       </c>
-      <c r="O146" s="19" t="n">
-        <v>10055.38</v>
-      </c>
-      <c r="P146" s="19" t="n">
-        <v>96.01000000000001</v>
+      <c r="O148" s="19" t="n">
+        <v>10282.88</v>
+      </c>
+      <c r="P148" s="19" t="n">
+        <v>95.45</v>
       </c>
     </row>
   </sheetData>
@@ -11158,6 +11284,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A144" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A145" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A146" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11732,26 +11860,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>19.75</v>
+        <v>20.25</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>0.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>15.75</v>
+        <v>17.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>15.8%</t>
         </is>
       </c>
     </row>
@@ -11762,7 +11890,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>25.75</v>
+        <v>26.25</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>2.5</v>
@@ -11771,7 +11899,7 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>28.75</v>
+        <v>29.25</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>7.5</v>
@@ -11781,7 +11909,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
     </row>
@@ -11793,7 +11921,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>34</v>
+        <v>40.75</v>
       </c>
     </row>
   </sheetData>
@@ -11878,19 +12006,19 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>403098</v>
+        <v>407345</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>205312</v>
+        <v>209560</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>197785</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>165176</v>
+        <v>163918</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>17470</v>
+        <v>18728</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>15139</v>
@@ -11903,10 +12031,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>185919</v>
+        <v>185691</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>80786</v>
+        <v>80558</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>105133</v>
@@ -11928,19 +12056,19 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>217179</v>
+        <v>221654</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>124527</v>
+        <v>129002</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>92652</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>68801</v>
+        <v>67544</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>12700</v>
+        <v>13957</v>
       </c>
       <c r="G7" s="27" t="n">
         <v>11151</v>
@@ -12120,7 +12248,7 @@
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>0</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="7">
@@ -12276,7 +12404,7 @@
         </is>
       </c>
       <c r="I10" s="25" t="n">
-        <v>3335</v>
+        <v>7810</v>
       </c>
     </row>
     <row r="11">
@@ -12318,7 +12446,7 @@
         </is>
       </c>
       <c r="I12" s="25" t="n">
-        <v>3335</v>
+        <v>7810</v>
       </c>
     </row>
   </sheetData>
